--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -132,18 +132,18 @@
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Full name of the employee." sqref="A2:A101">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B101">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B101">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." sqref="C2:C101">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." prompt="Enter a date between 2020-01-01 and 2030-12-31." sqref="C2:C101">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." sqref="D2:D101">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." prompt="Enter a number between 0 and 1000000." sqref="D2:D101">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="E2:E101">
+    <dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="E2:E101">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -132,18 +132,18 @@
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Full name of the employee." sqref="A2:A101">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="This field is required." sqref="B2:B101">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B101">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." prompt="Enter a date between 2020-01-01 and 2030-12-31." sqref="C2:C101">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." prompt="Date between 2020-01-01 and 2030-12-31" sqref="C2:C101">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." prompt="Enter a number between 0 and 1000000." sqref="D2:D101">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." prompt="Number between 0 and 1000000" sqref="D2:D101">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated." sqref="E2:E101">
+    <dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="E2:E101">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -132,18 +132,18 @@
     <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Full name of the employee." sqref="A2:A101">
       <formula1>LEN(TRIM(A2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="custom" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." sqref="B2:B101">
+    <dataValidation type="custom" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="This field is required." prompt="Required field" sqref="B2:B101">
       <formula1>LEN(TRIM(B2))&gt;0</formula1>
     </dataValidation>
-    <dataValidation type="date" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." sqref="C2:C101">
+    <dataValidation type="date" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Hire date must be on or after 2020-01-01." prompt="Date between 2020-01-01 and 2030-12-31" sqref="C2:C101">
       <formula1>43831</formula1>
       <formula2>47848</formula2>
     </dataValidation>
-    <dataValidation type="decimal" operator="between" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." sqref="D2:D101">
+    <dataValidation type="decimal" operator="between" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be a number between 0 and 1000000." prompt="Number between 0 and 1000000" sqref="D2:D101">
       <formula1>0</formula1>
       <formula2>1000000</formula2>
     </dataValidation>
-    <dataValidation type="list" allowBlank="0" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." sqref="E2:E101">
+    <dataValidation type="list" allowBlank="0" showInputMessage="1" showErrorMessage="1" errorTitle="Invalid value" error="Must be one of: Full Time, Part Time, Contract, Terminated." prompt="Select one of: Full Time, Part Time, Contract, Terminated" sqref="E2:E101">
       <formula1>"Full Time,Part Time,Contract,Terminated"</formula1>
     </dataValidation>
   </dataValidations>

--- a/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
+++ b/src/Excelsior.Tests/TemplateSheetTests.FullFeatured.verified.xlsx
@@ -151,7 +151,7 @@
 </file>
 
 <file path=customXml/item.xml><?xml version="1.0" encoding="utf-8"?>
-<columnMetadata xmlns="https://github.com/SimonCropp/Excelsior/columnMetadata/v1">
+<columnMetadata xmlns="https://github.com/Papyrine/Excelsior/columnMetadata/v1">
   <sheet name="Employees">
     <column index="1" property="Name"/>
     <column index="2" property="Email"/>
